--- a/finance/_refresh_uber-india.xlsx
+++ b/finance/_refresh_uber-india.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$30</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$30</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$27</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -717,7 +717,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Navier × Uber-India-Derivative — Corridor Unit Economics</t>
+          <t>Navier × Uber-India — Corridor Unit Economics</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,20 +1964,21 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Navier × Uber-India-Derivative — Corridor economics (one boat, one year; MID = headline)</t>
+          <t>Navier × Uber-India — Corridor economics (one boat, one year; MID = headline)</t>
         </is>
       </c>
       <c r="N1" s="28" t="inlineStr">
@@ -2208,40 +2209,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2250,7 +2256,7 @@
     <row r="4">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>India Kolkata Uber India Derivative</t>
+          <t>India Kolkata Uber India</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
@@ -2383,7 +2389,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2391,7 +2397,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2399,32 +2405,37 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="inlineStr">
+      <c r="AX4" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
         </is>
       </c>
-      <c r="AX4" s="44" t="n"/>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>India Kolkata Uber India Derivative</t>
+          <t>India Kolkata Uber India</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
@@ -2557,7 +2568,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2565,7 +2576,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2573,32 +2584,37 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="inlineStr">
+      <c r="AX5" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
         </is>
       </c>
-      <c r="AX5" s="44" t="n"/>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>India Kolkata Uber India Derivative</t>
+          <t>India Kolkata Uber India</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -2731,7 +2747,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2739,7 +2755,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2747,32 +2763,37 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="inlineStr">
+      <c r="AX6" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
         </is>
       </c>
-      <c r="AX6" s="44" t="n"/>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>India Kolkata Uber India Derivative</t>
+          <t>India Kolkata Uber India</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
@@ -2905,7 +2926,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2913,7 +2934,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2921,27 +2942,32 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="inlineStr">
+      <c r="AX7" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
         </is>
       </c>
-      <c r="AX7" s="44" t="n"/>
+      <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -2956,11 +2982,11 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>Bombay Harbour → Elephanta Caves</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="32" t="inlineStr">
@@ -3091,7 +3117,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3099,7 +3125,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3107,31 +3133,36 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
-      <c r="AR8" s="41" t="inlineStr">
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR8" s="41" t="n"/>
+      <c r="AS8" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="inlineStr">
+      <c r="AX8" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX8" s="44" t="inlineStr">
+      <c r="AY8" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -3140,7 +3171,7 @@
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Uber Mumbai</t>
+          <t>India Chennai Uber India</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
@@ -3150,23 +3181,17 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>Bombay Harbour → Elephanta Caves</t>
+          <t>Chennai Port WQIV Cruise Terminal → Marina Beach Waterfront</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
         <v>3.2</v>
       </c>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+      <c r="E9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
       <c r="H9" s="19" t="n">
         <v>1</v>
       </c>
@@ -3266,17 +3291,11 @@
         <f>((D9*O9/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D9*O9*VLOOKUP(B9,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG9" s="31" t="n"/>
-      <c r="AH9" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI9" s="32" t="inlineStr">
-        <is>
-          <t>partial-load-anchor-only</t>
-        </is>
-      </c>
+      <c r="AG9" s="31" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AH9" s="32" t="n"/>
+      <c r="AI9" s="32" t="n"/>
       <c r="AJ9" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3285,7 +3304,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3293,7 +3312,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3301,40 +3320,33 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
-      <c r="AR9" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
-      <c r="AS9" s="42" t="n"/>
-      <c r="AT9" s="43">
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR9" s="41" t="n"/>
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n"/>
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="inlineStr">
-        <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
-        </is>
-      </c>
-      <c r="AX9" s="44" t="inlineStr">
-        <is>
-          <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
-        </is>
-      </c>
+      <c r="AX9" s="44" t="n"/>
+      <c r="AY9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>India Chennai Uber India Derivative</t>
+          <t>Uber Mumbai</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -3344,17 +3356,23 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Chennai Port WQIV Cruise Terminal → Marina Beach Waterfront</t>
+          <t>Gateway of India → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="H10" s="19" t="n">
         <v>1</v>
       </c>
@@ -3454,11 +3472,17 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n">
-        <v>400000</v>
-      </c>
-      <c r="AH10" s="32" t="n"/>
-      <c r="AI10" s="32" t="n"/>
+      <c r="AG10" s="31" t="n"/>
+      <c r="AH10" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI10" s="32" t="inlineStr">
+        <is>
+          <t>partial-load-anchor-only</t>
+        </is>
+      </c>
       <c r="AJ10" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3467,7 +3491,7 @@
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3475,7 +3499,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3483,23 +3507,40 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
-      <c r="AT10" s="43">
+      <c r="AS10" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
+      <c r="AT10" s="42" t="n"/>
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="n"/>
-      <c r="AX10" s="44" t="n"/>
+      <c r="AX10" s="44" t="inlineStr">
+        <is>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+        </is>
+      </c>
+      <c r="AY10" s="44" t="inlineStr">
+        <is>
+          <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3514,11 +3555,11 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>Mora → Elephanta Caves</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E11" s="26" t="n"/>
       <c r="F11" s="32" t="inlineStr">
@@ -3649,7 +3690,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3657,7 +3698,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3665,31 +3706,36 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
-      <c r="AR11" s="41" t="inlineStr">
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR11" s="41" t="n"/>
+      <c r="AS11" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="inlineStr">
+      <c r="AX11" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX11" s="44" t="inlineStr">
+      <c r="AY11" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -3708,11 +3754,11 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>BSA Mandwa → Marina Bay Bistro @KARANJA Fishing Dock</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="32" t="inlineStr">
@@ -3843,7 +3889,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3851,7 +3897,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3859,31 +3905,36 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
-      <c r="AR12" s="41" t="inlineStr">
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR12" s="41" t="n"/>
+      <c r="AS12" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS12" s="42" t="n"/>
-      <c r="AT12" s="43">
+      <c r="AT12" s="42" t="n"/>
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="inlineStr">
+      <c r="AX12" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX12" s="44" t="inlineStr">
+      <c r="AY12" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -3902,11 +3953,11 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Mora → Elephanta Caves</t>
+          <t>Mandwa Jetty → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="32" t="inlineStr">
@@ -4037,7 +4088,7 @@
         <v/>
       </c>
       <c r="AL13" s="34">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),FLOOR(AK13/R13,1)))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
         <v/>
       </c>
       <c r="AM13" s="38">
@@ -4045,7 +4096,7 @@
         <v/>
       </c>
       <c r="AN13" s="36">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),AK13/R13))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
         <v/>
       </c>
       <c r="AO13" s="38">
@@ -4053,31 +4104,36 @@
         <v/>
       </c>
       <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="41" t="n"/>
-      <c r="AR13" s="41" t="inlineStr">
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR13" s="41" t="n"/>
+      <c r="AS13" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS13" s="42" t="n"/>
-      <c r="AT13" s="43">
+      <c r="AT13" s="42" t="n"/>
+      <c r="AU13" s="43">
         <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AU13" s="43">
+      <c r="AV13" s="43">
         <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AV13" s="43">
+      <c r="AW13" s="43">
         <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AW13" s="44" t="inlineStr">
+      <c r="AX13" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX13" s="44" t="inlineStr">
+      <c r="AY13" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -4096,11 +4152,11 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>BSA Mandwa → Marina Bay Bistro @KARANJA Fishing Dock</t>
+          <t>Elephanta Caves → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="32" t="inlineStr">
@@ -4231,7 +4287,7 @@
         <v/>
       </c>
       <c r="AL14" s="34">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),FLOOR(AK14/R14,1)))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
         <v/>
       </c>
       <c r="AM14" s="38">
@@ -4239,7 +4295,7 @@
         <v/>
       </c>
       <c r="AN14" s="36">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),AK14/R14))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
         <v/>
       </c>
       <c r="AO14" s="38">
@@ -4247,31 +4303,36 @@
         <v/>
       </c>
       <c r="AP14" s="40" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
-      <c r="AR14" s="41" t="inlineStr">
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR14" s="41" t="n"/>
+      <c r="AS14" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS14" s="42" t="n"/>
-      <c r="AT14" s="43">
+      <c r="AT14" s="42" t="n"/>
+      <c r="AU14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AU14" s="43">
+      <c r="AV14" s="43">
         <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AV14" s="43">
+      <c r="AW14" s="43">
         <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AW14" s="44" t="inlineStr">
+      <c r="AX14" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX14" s="44" t="inlineStr">
+      <c r="AY14" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -4290,11 +4351,11 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Mandwa Jetty → Mumbai Harbour</t>
+          <t>JNPT Ferry Service → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="32" t="inlineStr">
@@ -4425,7 +4486,7 @@
         <v/>
       </c>
       <c r="AL15" s="34">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),FLOOR(AK15/R15,1)))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
         <v/>
       </c>
       <c r="AM15" s="38">
@@ -4433,7 +4494,7 @@
         <v/>
       </c>
       <c r="AN15" s="36">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),AK15/R15))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
         <v/>
       </c>
       <c r="AO15" s="38">
@@ -4441,31 +4502,36 @@
         <v/>
       </c>
       <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="41" t="n"/>
-      <c r="AR15" s="41" t="inlineStr">
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR15" s="41" t="n"/>
+      <c r="AS15" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS15" s="42" t="n"/>
-      <c r="AT15" s="43">
+      <c r="AT15" s="42" t="n"/>
+      <c r="AU15" s="43">
         <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AU15" s="43">
+      <c r="AV15" s="43">
         <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AV15" s="43">
+      <c r="AW15" s="43">
         <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AW15" s="44" t="inlineStr">
+      <c r="AX15" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX15" s="44" t="inlineStr">
+      <c r="AY15" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -4484,11 +4550,11 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Elephanta Caves → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Pirpau Jetty → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="32" t="inlineStr">
@@ -4619,7 +4685,7 @@
         <v/>
       </c>
       <c r="AL16" s="34">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),FLOOR(AK16/R16,1)))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),FLOOR(AK16/R16,1)))</f>
         <v/>
       </c>
       <c r="AM16" s="38">
@@ -4627,7 +4693,7 @@
         <v/>
       </c>
       <c r="AN16" s="36">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),AK16/R16))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),AK16/R16))</f>
         <v/>
       </c>
       <c r="AO16" s="38">
@@ -4635,31 +4701,36 @@
         <v/>
       </c>
       <c r="AP16" s="40" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
-      <c r="AR16" s="41" t="inlineStr">
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR16" s="41" t="n"/>
+      <c r="AS16" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS16" s="42" t="n"/>
-      <c r="AT16" s="43">
+      <c r="AT16" s="42" t="n"/>
+      <c r="AU16" s="43">
         <f>IF(((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AU16" s="43">
+      <c r="AV16" s="43">
         <f>IF(((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AV16" s="43">
+      <c r="AW16" s="43">
         <f>IF(((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AW16" s="44" t="inlineStr">
+      <c r="AX16" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX16" s="44" t="inlineStr">
+      <c r="AY16" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -4678,11 +4749,11 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>JNPT Ferry Service → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Mumbai Harbour → Mandwa Jetty</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="32" t="inlineStr">
@@ -4813,7 +4884,7 @@
         <v/>
       </c>
       <c r="AL17" s="34">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),FLOOR(AK17/R17,1)))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),FLOOR(AK17/R17,1)))</f>
         <v/>
       </c>
       <c r="AM17" s="38">
@@ -4821,7 +4892,7 @@
         <v/>
       </c>
       <c r="AN17" s="36">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),AK17/R17))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),AK17/R17))</f>
         <v/>
       </c>
       <c r="AO17" s="38">
@@ -4829,31 +4900,36 @@
         <v/>
       </c>
       <c r="AP17" s="40" t="n"/>
-      <c r="AQ17" s="41" t="n"/>
-      <c r="AR17" s="41" t="inlineStr">
+      <c r="AQ17" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR17" s="41" t="n"/>
+      <c r="AS17" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS17" s="42" t="n"/>
-      <c r="AT17" s="43">
+      <c r="AT17" s="42" t="n"/>
+      <c r="AU17" s="43">
         <f>IF(((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AU17" s="43">
+      <c r="AV17" s="43">
         <f>IF(((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AV17" s="43">
+      <c r="AW17" s="43">
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AW17" s="44" t="inlineStr">
+      <c r="AX17" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX17" s="44" t="inlineStr">
+      <c r="AY17" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -4872,11 +4948,11 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Pirpau Jetty → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Versova Ferry Wharf → Gateway of India</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>6.2</v>
+        <v>12.43</v>
       </c>
       <c r="E18" s="26" t="n"/>
       <c r="F18" s="32" t="inlineStr">
@@ -5007,7 +5083,7 @@
         <v/>
       </c>
       <c r="AL18" s="34">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),FLOOR(AK18/R18,1)))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),FLOOR(AK18/R18,1)))</f>
         <v/>
       </c>
       <c r="AM18" s="38">
@@ -5015,7 +5091,7 @@
         <v/>
       </c>
       <c r="AN18" s="36">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),AK18/R18))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),AK18/R18))</f>
         <v/>
       </c>
       <c r="AO18" s="38">
@@ -5023,31 +5099,36 @@
         <v/>
       </c>
       <c r="AP18" s="40" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
-      <c r="AR18" s="41" t="inlineStr">
+      <c r="AQ18" s="32" t="inlineStr">
+        <is>
+          <t>Upside tier</t>
+        </is>
+      </c>
+      <c r="AR18" s="41" t="n"/>
+      <c r="AS18" s="41" t="inlineStr">
         <is>
           <t>experience_upside</t>
         </is>
       </c>
-      <c r="AS18" s="42" t="n"/>
-      <c r="AT18" s="43">
+      <c r="AT18" s="42" t="n"/>
+      <c r="AU18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AU18" s="43">
+      <c r="AV18" s="43">
         <f>IF(((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AV18" s="43">
+      <c r="AW18" s="43">
         <f>IF(((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AW18" s="44" t="inlineStr">
+      <c r="AX18" s="44" t="inlineStr">
         <is>
           <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
-      <c r="AX18" s="44" t="inlineStr">
+      <c r="AY18" s="44" t="inlineStr">
         <is>
           <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
         </is>
@@ -5056,7 +5137,7 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Uber Mumbai</t>
+          <t>India Kolkata Uber India</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
@@ -5066,23 +5147,17 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Mandwa Jetty → Mumbai Harbour</t>
+          <t>Millennium Park Jetty → Chandannagar Riverfront</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G19" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>17.9</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
       <c r="H19" s="19" t="n">
         <v>1</v>
       </c>
@@ -5182,17 +5257,11 @@
         <f>((D19*O19/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D19*O19*VLOOKUP(B19,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG19" s="31" t="n"/>
-      <c r="AH19" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI19" s="32" t="inlineStr">
-        <is>
-          <t>partial-load-anchor-only</t>
-        </is>
-      </c>
+      <c r="AG19" s="31" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AH19" s="32" t="n"/>
+      <c r="AI19" s="32" t="n"/>
       <c r="AJ19" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -5201,7 +5270,7 @@
         <v/>
       </c>
       <c r="AL19" s="34">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),FLOOR(AK19/R19,1)))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),FLOOR(AK19/R19,1)))</f>
         <v/>
       </c>
       <c r="AM19" s="38">
@@ -5209,7 +5278,7 @@
         <v/>
       </c>
       <c r="AN19" s="36">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),AK19/R19))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),AK19/R19))</f>
         <v/>
       </c>
       <c r="AO19" s="38">
@@ -5217,776 +5286,211 @@
         <v/>
       </c>
       <c r="AP19" s="40" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
-      <c r="AR19" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
-      <c r="AS19" s="42" t="n"/>
-      <c r="AT19" s="43">
+      <c r="AQ19" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR19" s="41" t="n"/>
+      <c r="AS19" s="41" t="n"/>
+      <c r="AT19" s="42" t="n"/>
+      <c r="AU19" s="43">
         <f>IF(((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AU19" s="43">
+      <c r="AV19" s="43">
         <f>IF(((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AV19" s="43">
+      <c r="AW19" s="43">
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AW19" s="44" t="inlineStr">
-        <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
-        </is>
-      </c>
       <c r="AX19" s="44" t="inlineStr">
         <is>
-          <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AY19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>TOTAL / median</t>
+        </is>
+      </c>
+      <c r="T20" s="46">
+        <f>SUM(T4:T19)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="46">
+        <f>SUM(AC4:AC19)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="47">
+        <f>IF(T20=0,"",AC20/T20)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="48">
+        <f>SUM(AL4:AL19)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="46">
+        <f>SUM(AM4:AM19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Fleet basis</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>Raw vessels (sum)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Fleet (rounded once)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>Market rev/yr (raw sum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>India Kolkata Uber India</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>network_sum</t>
+        </is>
+      </c>
+      <c r="C24" s="23">
+        <f>SUMIFS(AN4:AN19,A4:A19,"India Kolkata Uber India",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D24" s="49">
+        <f>ROUND(C24,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="50">
+        <f>SUMIFS(AO4:AO19,A4:A19,"India Kolkata Uber India",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Uber Mumbai</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <t>Mumbai Harbour → Mandwa Jetty</t>
-        </is>
-      </c>
-      <c r="D20" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G20" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="33">
-        <f>60*D20/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J20" s="33">
-        <f>I20+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K20" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
-        <v/>
-      </c>
-      <c r="L20" s="34">
-        <f>ROUND(365*mech_uptime*H20,0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N20" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O20" s="34">
-        <f>ROUND(K20*L20*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q20" s="36">
-        <f>pax_cap*P20</f>
-        <v/>
-      </c>
-      <c r="R20" s="34">
-        <f>Q20*O20</f>
-        <v/>
-      </c>
-      <c r="S20" s="37">
-        <f>E20*discount</f>
-        <v/>
-      </c>
-      <c r="T20" s="38">
-        <f>S20*R20</f>
-        <v/>
-      </c>
-      <c r="U20" s="38">
-        <f>(battery/range_nm)*D20*O20*VLOOKUP(B20,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V20" s="38">
-        <f>VLOOKUP(B20,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W20" s="38">
-        <f>VLOOKUP(B20,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X20" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y20" s="38">
-        <f>VLOOKUP(B20,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z20" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA20" s="38">
-        <f>U20+V20+W20+X20+Y20+Z20</f>
-        <v/>
-      </c>
-      <c r="AB20" s="38">
-        <f>VLOOKUP(B20,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC20" s="38">
-        <f>T20-AA20</f>
-        <v/>
-      </c>
-      <c r="AD20" s="35">
-        <f>IF(T20=0,"",AC20/T20)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="36">
-        <f>IF(AC20&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/AC20)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="33">
-        <f>((D20*O20/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D20*O20*VLOOKUP(B20,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG20" s="31" t="n"/>
-      <c r="AH20" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI20" s="32" t="inlineStr">
-        <is>
-          <t>partial-load-anchor-only</t>
-        </is>
-      </c>
-      <c r="AJ20" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK20" s="34">
-        <f>IF(AG20="","",AG20*AJ20)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="34">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),FLOOR(AK20/R20,1)))</f>
-        <v/>
-      </c>
-      <c r="AM20" s="38">
-        <f>IF(AL20="","",AL20*T20)</f>
-        <v/>
-      </c>
-      <c r="AN20" s="36">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),AK20/R20))</f>
-        <v/>
-      </c>
-      <c r="AO20" s="38">
-        <f>IF(AN20="","",AN20*T20)</f>
-        <v/>
-      </c>
-      <c r="AP20" s="40" t="n"/>
-      <c r="AQ20" s="41" t="n"/>
-      <c r="AR20" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
-      <c r="AS20" s="42" t="n"/>
-      <c r="AT20" s="43">
-        <f>IF(((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
-        <v/>
-      </c>
-      <c r="AU20" s="43">
-        <f>IF(((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
-        <v/>
-      </c>
-      <c r="AV20" s="43">
-        <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
-        <v/>
-      </c>
-      <c r="AW20" s="44" t="inlineStr">
-        <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
-        </is>
-      </c>
-      <c r="AX20" s="44" t="inlineStr">
-        <is>
-          <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>Uber Mumbai</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>Versova Ferry Wharf → Gateway of India</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G21" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="33">
-        <f>60*D21/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J21" s="33">
-        <f>I21+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K21" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
-        <v/>
-      </c>
-      <c r="L21" s="34">
-        <f>ROUND(365*mech_uptime*H21,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N21" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O21" s="34">
-        <f>ROUND(K21*L21*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q21" s="36">
-        <f>pax_cap*P21</f>
-        <v/>
-      </c>
-      <c r="R21" s="34">
-        <f>Q21*O21</f>
-        <v/>
-      </c>
-      <c r="S21" s="37">
-        <f>E21*discount</f>
-        <v/>
-      </c>
-      <c r="T21" s="38">
-        <f>S21*R21</f>
-        <v/>
-      </c>
-      <c r="U21" s="38">
-        <f>(battery/range_nm)*D21*O21*VLOOKUP(B21,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V21" s="38">
-        <f>VLOOKUP(B21,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W21" s="38">
-        <f>VLOOKUP(B21,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X21" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y21" s="38">
-        <f>VLOOKUP(B21,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z21" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA21" s="38">
-        <f>U21+V21+W21+X21+Y21+Z21</f>
-        <v/>
-      </c>
-      <c r="AB21" s="38">
-        <f>VLOOKUP(B21,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC21" s="38">
-        <f>T21-AA21</f>
-        <v/>
-      </c>
-      <c r="AD21" s="35">
-        <f>IF(T21=0,"",AC21/T21)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="36">
-        <f>IF(AC21&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/AC21)</f>
-        <v/>
-      </c>
-      <c r="AF21" s="33">
-        <f>((D21*O21/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D21*O21*VLOOKUP(B21,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG21" s="31" t="n"/>
-      <c r="AH21" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI21" s="32" t="inlineStr">
-        <is>
-          <t>partial-load-anchor-only</t>
-        </is>
-      </c>
-      <c r="AJ21" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK21" s="34">
-        <f>IF(AG21="","",AG21*AJ21)</f>
-        <v/>
-      </c>
-      <c r="AL21" s="34">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),FLOOR(AK21/R21,1)))</f>
-        <v/>
-      </c>
-      <c r="AM21" s="38">
-        <f>IF(AL21="","",AL21*T21)</f>
-        <v/>
-      </c>
-      <c r="AN21" s="36">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),AK21/R21))</f>
-        <v/>
-      </c>
-      <c r="AO21" s="38">
-        <f>IF(AN21="","",AN21*T21)</f>
-        <v/>
-      </c>
-      <c r="AP21" s="40" t="n"/>
-      <c r="AQ21" s="41" t="n"/>
-      <c r="AR21" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
-      <c r="AS21" s="42" t="n"/>
-      <c r="AT21" s="43">
-        <f>IF(((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
-        <v/>
-      </c>
-      <c r="AU21" s="43">
-        <f>IF(((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
-        <v/>
-      </c>
-      <c r="AV21" s="43">
-        <f>IF(((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
-        <v/>
-      </c>
-      <c r="AW21" s="44" t="inlineStr">
-        <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
-        </is>
-      </c>
-      <c r="AX21" s="44" t="inlineStr">
-        <is>
-          <t>Mumbai water taxi demand anchors: Indian Express (2023-02-08) reported Nayantara/NAYAN XI 200-seat DCT→Mandwa via Belapur had poor DCT ridership but averaged 120 passengers from Belapur; fares ₹400 lower deck/₹450 upper/business. The Hindu (2022-11-13) reported Belapur→Elephanta filling ~80% capacity on a 32-seat vessel with three round trips, Belapur→JNPT doing well, and DCT→Mandwa 60 round trips in 10 days with &lt;10% occupancy on 200-seat vessel. These are direct observed load/service-health anchors, not annual passenger counts; annual demand remains null.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>India Kolkata Uber India Derivative</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C22" s="30" t="inlineStr">
-        <is>
-          <t>Millennium Park Jetty → Chandannagar Riverfront</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="32" t="n"/>
-      <c r="H22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="33">
-        <f>60*D22/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J22" s="33">
-        <f>I22+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K22" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
-        <v/>
-      </c>
-      <c r="L22" s="34">
-        <f>ROUND(365*mech_uptime*H22,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N22" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O22" s="34">
-        <f>ROUND(K22*L22*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q22" s="36">
-        <f>pax_cap*P22</f>
-        <v/>
-      </c>
-      <c r="R22" s="34">
-        <f>Q22*O22</f>
-        <v/>
-      </c>
-      <c r="S22" s="37">
-        <f>E22*discount</f>
-        <v/>
-      </c>
-      <c r="T22" s="38">
-        <f>S22*R22</f>
-        <v/>
-      </c>
-      <c r="U22" s="38">
-        <f>(battery/range_nm)*D22*O22*VLOOKUP(B22,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V22" s="38">
-        <f>VLOOKUP(B22,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W22" s="38">
-        <f>VLOOKUP(B22,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X22" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y22" s="38">
-        <f>VLOOKUP(B22,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z22" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA22" s="38">
-        <f>U22+V22+W22+X22+Y22+Z22</f>
-        <v/>
-      </c>
-      <c r="AB22" s="38">
-        <f>VLOOKUP(B22,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC22" s="38">
-        <f>T22-AA22</f>
-        <v/>
-      </c>
-      <c r="AD22" s="35">
-        <f>IF(T22=0,"",AC22/T22)</f>
-        <v/>
-      </c>
-      <c r="AE22" s="36">
-        <f>IF(AC22&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/AC22)</f>
-        <v/>
-      </c>
-      <c r="AF22" s="33">
-        <f>((D22*O22/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D22*O22*VLOOKUP(B22,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG22" s="31" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="AH22" s="32" t="n"/>
-      <c r="AI22" s="32" t="n"/>
-      <c r="AJ22" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK22" s="34">
-        <f>IF(AG22="","",AG22*AJ22)</f>
-        <v/>
-      </c>
-      <c r="AL22" s="34">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),FLOOR(AK22/R22,1)))</f>
-        <v/>
-      </c>
-      <c r="AM22" s="38">
-        <f>IF(AL22="","",AL22*T22)</f>
-        <v/>
-      </c>
-      <c r="AN22" s="36">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),AK22/R22))</f>
-        <v/>
-      </c>
-      <c r="AO22" s="38">
-        <f>IF(AN22="","",AN22*T22)</f>
-        <v/>
-      </c>
-      <c r="AP22" s="40" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
-      <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="42" t="n"/>
-      <c r="AT22" s="43">
-        <f>IF(((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
-        <v/>
-      </c>
-      <c r="AU22" s="43">
-        <f>IF(((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
-        <v/>
-      </c>
-      <c r="AV22" s="43">
-        <f>IF(((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
-        <v/>
-      </c>
-      <c r="AW22" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
-        </is>
-      </c>
-      <c r="AX22" s="44" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL / median</t>
-        </is>
-      </c>
-      <c r="T23" s="46">
-        <f>SUM(T4:T22)</f>
-        <v/>
-      </c>
-      <c r="AC23" s="46">
-        <f>SUM(AC4:AC22)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="47">
-        <f>IF(T23=0,"",AC23/T23)</f>
-        <v/>
-      </c>
-      <c r="AL23" s="48">
-        <f>SUM(AL4:AL22)</f>
-        <v/>
-      </c>
-      <c r="AM23" s="46">
-        <f>SUM(AM4:AM22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
-        </is>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>per_corridor_floor</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="49">
+        <f>SUMIFS(AL4:AL19,A4:A19,"Uber Mumbai",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E25" s="50">
+        <f>SUMIFS(AM4:AM19,A4:A19,"Uber Mumbai",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Fleet basis</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Raw vessels (sum)</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>Fleet (rounded once)</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>Market rev/yr (raw sum)</t>
-        </is>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>India Chennai Uber India</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>network_sum</t>
+        </is>
+      </c>
+      <c r="C26" s="23">
+        <f>SUMIFS(AN4:AN19,A4:A19,"India Chennai Uber India",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D26" s="49">
+        <f>ROUND(C26,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="50">
+        <f>SUMIFS(AO4:AO19,A4:A19,"India Chennai Uber India",AP4:AP19,"=",AQ4:AQ19,"Grounded")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>India Kolkata Uber India Derivative</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>network_sum</t>
-        </is>
-      </c>
-      <c r="C27" s="23">
-        <f>SUMIFS(AN4:AN22,A4:A22,"India Kolkata Uber India Derivative",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
-        <v/>
-      </c>
-      <c r="D27" s="49">
-        <f>ROUND(C27,0)</f>
-        <v/>
-      </c>
-      <c r="E27" s="50">
-        <f>SUMIFS(AO4:AO22,A4:A22,"India Kolkata Uber India Derivative",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>GROUNDED FLOOR (PUBLISHED)</t>
+        </is>
+      </c>
+      <c r="D27" s="48">
+        <f>SUM(D24:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="46">
+        <f>SUM(E24:E26)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Uber Mumbai</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>per_corridor_floor</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="49">
-        <f>SUMIFS(AL4:AL22,A4:A22,"Uber Mumbai",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
-        <v/>
-      </c>
-      <c r="E28" s="50">
-        <f>SUMIFS(AM4:AM22,A4:A22,"Uber Mumbai",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>India Chennai Uber India Derivative</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>network_sum</t>
-        </is>
-      </c>
-      <c r="C29" s="23">
-        <f>SUMIFS(AN4:AN22,A4:A22,"India Chennai Uber India Derivative",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
-        <v/>
-      </c>
-      <c r="D29" s="49">
-        <f>ROUND(C29,0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="50">
-        <f>SUMIFS(AO4:AO22,A4:A22,"India Chennai Uber India Derivative",AP4:AP22,"=",AQ4:AQ22,"=",AR4:AR22,"=")</f>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED UPSIDE (LB-99 modal-shift / experience-upside tiers; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D28" s="51">
+        <f>SUMIF(AQ4:AQ19,"Upside tier",AL4:AL19)</f>
+        <v/>
+      </c>
+      <c r="E28" s="52">
+        <f>SUMIF(AQ4:AQ19,"Upside tier",AM4:AM19)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>GROUNDED FLOOR (PUBLISHED)</t>
-        </is>
-      </c>
-      <c r="D30" s="48">
-        <f>SUM(D27:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="46">
-        <f>SUM(E27:E29)</f>
-        <v/>
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
+        </is>
+      </c>
+      <c r="C30" s="54" t="inlineStr">
+        <is>
+          <t>Chennai Port WQIV Cruise Terminal → Cuddalore Port (90.0nm)</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>ESTIMATED UPSIDE (LB-99 modal-shift / experience-upside tiers; held OUT of grounded floor)</t>
-        </is>
-      </c>
-      <c r="D31" s="51">
-        <f>SUMIF(AR4:AR22,"&lt;&gt;",AL4:AL22)</f>
-        <v/>
-      </c>
-      <c r="E31" s="52">
-        <f>SUMIF(AR4:AR22,"&lt;&gt;",AM4:AM22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="53" t="inlineStr">
-        <is>
-          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
-        </is>
-      </c>
-      <c r="C33" s="54" t="inlineStr">
-        <is>
-          <t>Chennai Port WQIV Cruise Terminal → Cuddalore Port (90.0nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" s="54" t="inlineStr">
+      <c r="C31" s="54" t="inlineStr">
         <is>
           <t>Chennai Port WQIV Cruise Terminal → Puducherry Port (76.6nm)</t>
         </is>
@@ -5994,8 +5498,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A25:L25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6218,7 +5722,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
